--- a/section9_kinetics/C1/c1_data.xlsx
+++ b/section9_kinetics/C1/c1_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/mayerlab_files/Stefan/Paper2025/raw_data_2025_09_05/C1_acetaldehyde/analysis_2025_09_30_pKa_corr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefan/Documents/Publikationen/06:25/WaterHTE-main/section9_kinetics/C1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FD1518-657A-3A44-9A74-C18A01CA2883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0DA831-FF00-6D4A-8720-45D210926E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4100" yWindow="-21100" windowWidth="38400" windowHeight="19500" xr2:uid="{4157E0E5-6C1F-1B4B-A595-D7C72E098651}"/>
+    <workbookView xWindow="-4100" yWindow="-21000" windowWidth="38400" windowHeight="19500" xr2:uid="{4157E0E5-6C1F-1B4B-A595-D7C72E098651}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -30630,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="J322">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K322">
         <v>9.15</v>
@@ -30719,7 +30719,7 @@
         <v>1</v>
       </c>
       <c r="J323">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K323">
         <v>9.15</v>
@@ -30808,7 +30808,7 @@
         <v>1</v>
       </c>
       <c r="J324">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K324">
         <v>9.15</v>
@@ -30897,7 +30897,7 @@
         <v>1</v>
       </c>
       <c r="J325">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K325">
         <v>9.15</v>
@@ -30986,7 +30986,7 @@
         <v>1</v>
       </c>
       <c r="J326">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K326">
         <v>9.15</v>
@@ -31075,7 +31075,7 @@
         <v>1</v>
       </c>
       <c r="J327">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K327">
         <v>9.15</v>
@@ -31164,7 +31164,7 @@
         <v>1</v>
       </c>
       <c r="J328">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K328">
         <v>9.15</v>
@@ -31253,7 +31253,7 @@
         <v>1</v>
       </c>
       <c r="J329">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K329">
         <v>9.15</v>
@@ -31342,7 +31342,7 @@
         <v>1</v>
       </c>
       <c r="J330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K330">
         <v>9.15</v>
@@ -31431,7 +31431,7 @@
         <v>1</v>
       </c>
       <c r="J331">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K331">
         <v>9.15</v>
@@ -31520,7 +31520,7 @@
         <v>1</v>
       </c>
       <c r="J332">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K332">
         <v>9.15</v>
@@ -31609,7 +31609,7 @@
         <v>1</v>
       </c>
       <c r="J333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K333">
         <v>9.15</v>
@@ -31698,7 +31698,7 @@
         <v>1</v>
       </c>
       <c r="J334">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K334">
         <v>9.15</v>
@@ -31787,7 +31787,7 @@
         <v>1</v>
       </c>
       <c r="J335">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K335">
         <v>9.15</v>
@@ -31876,7 +31876,7 @@
         <v>1</v>
       </c>
       <c r="J336">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K336">
         <v>9.15</v>
@@ -31965,7 +31965,7 @@
         <v>1</v>
       </c>
       <c r="J337">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K337">
         <v>9.15</v>
@@ -32054,7 +32054,7 @@
         <v>1</v>
       </c>
       <c r="J338">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K338">
         <v>9.64</v>
@@ -32143,7 +32143,7 @@
         <v>1</v>
       </c>
       <c r="J339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K339">
         <v>9.64</v>
@@ -32232,7 +32232,7 @@
         <v>1</v>
       </c>
       <c r="J340">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K340">
         <v>9.64</v>
@@ -32321,7 +32321,7 @@
         <v>1</v>
       </c>
       <c r="J341">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K341">
         <v>9.64</v>
@@ -32410,7 +32410,7 @@
         <v>1</v>
       </c>
       <c r="J342">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K342">
         <v>9.64</v>
@@ -32499,7 +32499,7 @@
         <v>1</v>
       </c>
       <c r="J343">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K343">
         <v>9.64</v>
@@ -32588,7 +32588,7 @@
         <v>1</v>
       </c>
       <c r="J344">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K344">
         <v>9.64</v>
@@ -32677,7 +32677,7 @@
         <v>1</v>
       </c>
       <c r="J345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K345">
         <v>9.64</v>
@@ -32766,7 +32766,7 @@
         <v>1</v>
       </c>
       <c r="J346">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K346">
         <v>9.64</v>
@@ -32855,7 +32855,7 @@
         <v>1</v>
       </c>
       <c r="J347">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K347">
         <v>9.64</v>
@@ -32944,7 +32944,7 @@
         <v>1</v>
       </c>
       <c r="J348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K348">
         <v>9.64</v>
@@ -33033,7 +33033,7 @@
         <v>1</v>
       </c>
       <c r="J349">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K349">
         <v>9.64</v>
@@ -33122,7 +33122,7 @@
         <v>1</v>
       </c>
       <c r="J350">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K350">
         <v>9.64</v>
@@ -33211,7 +33211,7 @@
         <v>1</v>
       </c>
       <c r="J351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K351">
         <v>9.64</v>
@@ -33300,7 +33300,7 @@
         <v>1</v>
       </c>
       <c r="J352">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K352">
         <v>9.64</v>
@@ -33389,7 +33389,7 @@
         <v>1</v>
       </c>
       <c r="J353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K353">
         <v>9.64</v>
@@ -33478,7 +33478,7 @@
         <v>1</v>
       </c>
       <c r="J354">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K354">
         <v>10.07</v>
@@ -33567,7 +33567,7 @@
         <v>1</v>
       </c>
       <c r="J355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K355">
         <v>10.07</v>
@@ -33656,7 +33656,7 @@
         <v>1</v>
       </c>
       <c r="J356">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K356">
         <v>10.07</v>
@@ -33745,7 +33745,7 @@
         <v>1</v>
       </c>
       <c r="J357">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K357">
         <v>10.07</v>
@@ -33834,7 +33834,7 @@
         <v>1</v>
       </c>
       <c r="J358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K358">
         <v>10.07</v>
@@ -33923,7 +33923,7 @@
         <v>1</v>
       </c>
       <c r="J359">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K359">
         <v>10.07</v>
@@ -34012,7 +34012,7 @@
         <v>1</v>
       </c>
       <c r="J360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K360">
         <v>10.07</v>
@@ -34101,7 +34101,7 @@
         <v>1</v>
       </c>
       <c r="J361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K361">
         <v>10.07</v>
@@ -34190,7 +34190,7 @@
         <v>1</v>
       </c>
       <c r="J362">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K362">
         <v>10.07</v>
@@ -34279,7 +34279,7 @@
         <v>1</v>
       </c>
       <c r="J363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K363">
         <v>10.07</v>
@@ -34368,7 +34368,7 @@
         <v>1</v>
       </c>
       <c r="J364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K364">
         <v>10.07</v>
@@ -34457,7 +34457,7 @@
         <v>1</v>
       </c>
       <c r="J365">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K365">
         <v>10.07</v>
@@ -34546,7 +34546,7 @@
         <v>1</v>
       </c>
       <c r="J366">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K366">
         <v>10.07</v>
@@ -34635,7 +34635,7 @@
         <v>1</v>
       </c>
       <c r="J367">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K367">
         <v>10.07</v>
@@ -34724,7 +34724,7 @@
         <v>1</v>
       </c>
       <c r="J368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K368">
         <v>10.07</v>
@@ -34813,7 +34813,7 @@
         <v>1</v>
       </c>
       <c r="J369">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K369">
         <v>10.07</v>
@@ -34902,7 +34902,7 @@
         <v>1</v>
       </c>
       <c r="J370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K370">
         <v>10.43</v>
@@ -34991,7 +34991,7 @@
         <v>1</v>
       </c>
       <c r="J371">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K371">
         <v>10.43</v>
@@ -35080,7 +35080,7 @@
         <v>1</v>
       </c>
       <c r="J372">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K372">
         <v>10.43</v>
@@ -35169,7 +35169,7 @@
         <v>1</v>
       </c>
       <c r="J373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K373">
         <v>10.43</v>
@@ -35258,7 +35258,7 @@
         <v>1</v>
       </c>
       <c r="J374">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K374">
         <v>10.43</v>
@@ -35347,7 +35347,7 @@
         <v>1</v>
       </c>
       <c r="J375">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K375">
         <v>10.43</v>
@@ -35436,7 +35436,7 @@
         <v>1</v>
       </c>
       <c r="J376">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K376">
         <v>10.43</v>
@@ -35525,7 +35525,7 @@
         <v>1</v>
       </c>
       <c r="J377">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K377">
         <v>10.43</v>
@@ -35614,7 +35614,7 @@
         <v>1</v>
       </c>
       <c r="J378">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K378">
         <v>10.43</v>
@@ -35703,7 +35703,7 @@
         <v>1</v>
       </c>
       <c r="J379">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K379">
         <v>10.43</v>
@@ -35792,7 +35792,7 @@
         <v>1</v>
       </c>
       <c r="J380">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K380">
         <v>10.43</v>
@@ -35881,7 +35881,7 @@
         <v>1</v>
       </c>
       <c r="J381">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K381">
         <v>10.43</v>
@@ -35970,7 +35970,7 @@
         <v>1</v>
       </c>
       <c r="J382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K382">
         <v>10.43</v>
@@ -36059,7 +36059,7 @@
         <v>1</v>
       </c>
       <c r="J383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K383">
         <v>10.43</v>
@@ -36148,7 +36148,7 @@
         <v>1</v>
       </c>
       <c r="J384">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K384">
         <v>10.43</v>
@@ -36237,7 +36237,7 @@
         <v>1</v>
       </c>
       <c r="J385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K385">
         <v>10.43</v>
